--- a/data/trans_camb/P2A_fisi_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 9,32</t>
+          <t>1,02; 8,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 6,39</t>
+          <t>-0,69; 6,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 10,88</t>
+          <t>2,84; 11,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,27; 15,54</t>
+          <t>6,17; 15,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 10,67</t>
+          <t>2,76; 10,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 11,57</t>
+          <t>4,73; 11,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,9; 10,72</t>
+          <t>4,94; 10,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,42</t>
+          <t>2,15; 7,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 10,26</t>
+          <t>4,69; 9,98</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,16; 622,27</t>
+          <t>10,03; 670,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 565,9</t>
+          <t>-22,61; 475,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,63; 735,3</t>
+          <t>40,95; 755,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>142,84; 1455,01</t>
+          <t>129,68; 1387,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45,98; 888,1</t>
+          <t>49,37; 896,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>98,53; 1196,6</t>
+          <t>91,12; 974,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>129,44; 646,48</t>
+          <t>109,11; 587,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,08; 424,61</t>
+          <t>57,46; 437,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>127,07; 624,06</t>
+          <t>107,84; 591,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 4,0</t>
+          <t>-3,2; 4,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,56; -1,5</t>
+          <t>-7,41; -1,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 13,96</t>
+          <t>4,62; 14,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 3,98</t>
+          <t>-3,27; 3,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,35; -0,98</t>
+          <t>-6,74; -0,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 11,03</t>
+          <t>4,38; 11,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 2,66</t>
+          <t>-2,16; 2,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,23; -2,02</t>
+          <t>-6,36; -2,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 11,25</t>
+          <t>5,68; 11,3</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,21; 65,23</t>
+          <t>-33,93; 72,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-76,9; -18,81</t>
+          <t>-77,56; -26,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,65; 230,42</t>
+          <t>48,64; 236,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,81; 65,46</t>
+          <t>-35,04; 63,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,94; -14,66</t>
+          <t>-71,59; -11,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,22; 182,21</t>
+          <t>43,88; 197,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 40,19</t>
+          <t>-24,47; 41,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,8; -28,99</t>
+          <t>-68,63; -29,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59,19; 169,29</t>
+          <t>62,7; 176,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 9,39</t>
+          <t>1,92; 9,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 1,6</t>
+          <t>-2,65; 1,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,81; 14,55</t>
+          <t>7,12; 14,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 8,61</t>
+          <t>1,64; 8,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 3,35</t>
+          <t>-1,91; 3,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 11,26</t>
+          <t>4,7; 11,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,87</t>
+          <t>2,89; 7,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,72</t>
+          <t>-1,68; 1,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,79; 12,03</t>
+          <t>6,94; 11,87</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41,18; 769,39</t>
+          <t>42,22; 713,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-78,75; 179,59</t>
+          <t>-77,94; 201,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>188,94; 1329,79</t>
+          <t>184,77; 1456,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27,97; 523,62</t>
+          <t>34,59; 530,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,3; 225,93</t>
+          <t>-51,27; 223,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>86,61; 671,65</t>
+          <t>95,81; 736,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>72,94; 481,6</t>
+          <t>74,73; 440,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,79; 108,65</t>
+          <t>-49,71; 102,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>180,79; 726,15</t>
+          <t>176,53; 692,19</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,93</t>
+          <t>0,9; 6,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 9,59</t>
+          <t>2,87; 9,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 9,31</t>
+          <t>1,21; 8,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 8,23</t>
+          <t>0,66; 8,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 10,13</t>
+          <t>2,07; 10,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 1,8</t>
+          <t>-4,27; 1,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,41</t>
+          <t>1,49; 6,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,42; 8,72</t>
+          <t>3,33; 9,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,83</t>
+          <t>-0,83; 3,95</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,06; 550,68</t>
+          <t>20,67; 524,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>72,5; 743,25</t>
+          <t>78,51; 723,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,6; 651,72</t>
+          <t>30,22; 696,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,85; 234,1</t>
+          <t>7,06; 233,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,42; 271,89</t>
+          <t>26,15; 288,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,65; 52,16</t>
+          <t>-61,37; 56,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,98; 227,44</t>
+          <t>27,94; 230,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>67,74; 309,57</t>
+          <t>64,12; 316,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-23,11; 140,41</t>
+          <t>-19,02; 143,36</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 11,73</t>
+          <t>-0,88; 11,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 3,83</t>
+          <t>-5,91; 4,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 3,79</t>
+          <t>-5,75; 3,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,26; 16,75</t>
+          <t>3,29; 16,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 2,08</t>
+          <t>-8,21; 2,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 1,77</t>
+          <t>-9,22; 1,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,6; 12,21</t>
+          <t>3,12; 12,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 1,93</t>
+          <t>-5,86; 1,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 1,27</t>
+          <t>-5,96; 1,22</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 206,18</t>
+          <t>-11,68; 191,96</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-57,25; 65,01</t>
+          <t>-55,67; 85,64</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-51,81; 62,12</t>
+          <t>-52,84; 71,38</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21,86; 245,16</t>
+          <t>20,95; 243,16</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-64,25; 33,56</t>
+          <t>-64,67; 35,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-64,03; 25,44</t>
+          <t>-64,88; 27,48</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,37; 176,9</t>
+          <t>24,9; 168,0</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-50,91; 29,62</t>
+          <t>-53,46; 30,87</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-49,51; 17,53</t>
+          <t>-51,83; 16,62</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,2; 8,25</t>
+          <t>2,57; 8,67</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,81; 11,57</t>
+          <t>4,29; 11,52</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16,23; 25,9</t>
+          <t>16,15; 25,06</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,41; 12,82</t>
+          <t>4,32; 12,95</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,86; 11,22</t>
+          <t>2,61; 11,21</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,81; 21,47</t>
+          <t>12,8; 21,46</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,54; 9,75</t>
+          <t>4,57; 9,82</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>4,71; 10,29</t>
+          <t>4,59; 10,29</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>15,9; 22,1</t>
+          <t>15,74; 21,88</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>76,35; —</t>
+          <t>44,85; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>209,16; —</t>
+          <t>208,36; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>789,86; —</t>
+          <t>747,81; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>101,3; 934,07</t>
+          <t>93,9; 929,76</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>58,47; 806,52</t>
+          <t>48,15; 814,88</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>275,36; 1618,8</t>
+          <t>276,61; 1581,83</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>153,59; 930,79</t>
+          <t>155,84; 1020,67</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>147,39; 955,2</t>
+          <t>171,37; 1076,21</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>547,99; 2470,59</t>
+          <t>557,99; 2586,94</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,92</t>
+          <t>-1,67; 3,69</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 0,73</t>
+          <t>-3,91; 0,92</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,3; 8,58</t>
+          <t>2,58; 8,45</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 4,8</t>
+          <t>-0,85; 5,11</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 3,0</t>
+          <t>-2,26; 3,1</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,38; 60,15</t>
+          <t>6,53; 61,91</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,7</t>
+          <t>-0,45; 3,69</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 1,28</t>
+          <t>-2,45; 1,38</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,78; 48,41</t>
+          <t>5,58; 44,69</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-22,91; 84,56</t>
+          <t>-23,96; 85,27</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-58,1; 17,51</t>
+          <t>-56,11; 25,35</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29,45; 192,89</t>
+          <t>34,92; 184,37</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 108,08</t>
+          <t>-14,17; 111,91</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-32,83; 70,07</t>
+          <t>-31,4; 72,72</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>104,9; 1884,66</t>
+          <t>103,12; 1319,78</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 77,69</t>
+          <t>-7,6; 76,34</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 27,91</t>
+          <t>-35,67; 30,32</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>93,52; 991,62</t>
+          <t>92,58; 895,78</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 2,56</t>
+          <t>-2,58; 2,69</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 3,0</t>
+          <t>-2,46; 2,89</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 0,73</t>
+          <t>-6,01; 0,95</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,74; -0,08</t>
+          <t>-5,97; -0,48</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 1,12</t>
+          <t>-5,0; 1,01</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 1,63</t>
+          <t>-4,03; 1,45</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,28</t>
+          <t>-3,41; 0,39</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,21</t>
+          <t>-2,77; 1,37</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 0,22</t>
+          <t>-4,55; 0,32</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-33,9; 48,05</t>
+          <t>-32,6; 52,09</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-33,11; 54,98</t>
+          <t>-30,71; 54,2</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-70,72; 12,92</t>
+          <t>-73,7; 14,87</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-52,93; -0,07</t>
+          <t>-55,46; -4,98</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-45,14; 14,59</t>
+          <t>-45,66; 13,37</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-33,0; 21,07</t>
+          <t>-35,25; 18,5</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 3,15</t>
+          <t>-38,47; 5,99</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-29,11; 17,4</t>
+          <t>-30,92; 18,19</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-53,33; 1,43</t>
+          <t>-51,35; 3,12</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,57</t>
+          <t>1,02; 3,39</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,64</t>
+          <t>-0,78; 1,62</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,96</t>
+          <t>3,22; 6,95</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,12</t>
+          <t>1,48; 4,19</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,8</t>
+          <t>-0,58; 1,92</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,17; 25,27</t>
+          <t>4,22; 24,02</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,41</t>
+          <t>1,74; 3,56</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,41</t>
+          <t>-0,29; 1,46</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>4,62; 17,2</t>
+          <t>4,66; 15,84</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>21,43; 79,23</t>
+          <t>17,2; 76,62</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 37,67</t>
+          <t>-13,72; 36,56</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>58,69; 154,49</t>
+          <t>62,04; 154,33</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>22,25; 73,1</t>
+          <t>20,45; 73,41</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 31,97</t>
+          <t>-8,84; 33,54</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>64,01; 422,49</t>
+          <t>66,08; 418,22</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>29,21; 66,27</t>
+          <t>28,35; 67,2</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 27,01</t>
+          <t>-4,87; 27,8</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>79,18; 323,21</t>
+          <t>80,62; 298,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_fisi_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,71</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,19</t>
+          <t>7,7</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,42</t>
+          <t>6,84</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 8,7</t>
+          <t>1,29; 9,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 6,38</t>
+          <t>-0,65; 6,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 11,25</t>
+          <t>2,33; 10,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,17; 15,82</t>
+          <t>6,52; 15,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 10,63</t>
+          <t>2,47; 10,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,73; 11,63</t>
+          <t>4,48; 10,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 10,72</t>
+          <t>4,87; 10,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 7,49</t>
+          <t>1,92; 7,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,69; 9,98</t>
+          <t>4,66; 9,47</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>236,07%</t>
+          <t>210,87%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>344,77%</t>
+          <t>324,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>284,06%</t>
+          <t>261,67%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,03; 670,7</t>
+          <t>15,77; 749,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,61; 475,69</t>
+          <t>-22,82; 497,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,95; 755,53</t>
+          <t>36,11; 645,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>129,68; 1387,13</t>
+          <t>145,11; 1572,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,37; 896,51</t>
+          <t>42,77; 969,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,12; 974,63</t>
+          <t>96,05; 989,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>109,11; 587,24</t>
+          <t>113,42; 646,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>57,46; 437,53</t>
+          <t>41,33; 478,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>107,84; 591,72</t>
+          <t>112,41; 618,89</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,28</t>
+          <t>9,23</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,62</t>
+          <t>7,47</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,45</t>
+          <t>8,34</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 4,23</t>
+          <t>-3,65; 3,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,41; -1,59</t>
+          <t>-7,91; -1,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 14,23</t>
+          <t>4,75; 14,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 3,91</t>
+          <t>-3,33; 3,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,74; -0,72</t>
+          <t>-7,19; -0,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 11,28</t>
+          <t>4,04; 10,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,91</t>
+          <t>-2,18; 3,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,36; -2,1</t>
+          <t>-6,17; -1,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,68; 11,3</t>
+          <t>5,74; 11,09</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>118,56%</t>
+          <t>117,98%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>108,47%</t>
+          <t>106,98%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,93; 72,89</t>
+          <t>-36,97; 65,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-77,56; -26,12</t>
+          <t>-78,05; -23,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,64; 236,78</t>
+          <t>48,44; 235,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,04; 63,13</t>
+          <t>-35,41; 56,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-71,59; -11,46</t>
+          <t>-70,48; -8,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,88; 197,96</t>
+          <t>38,69; 177,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,47; 41,34</t>
+          <t>-24,45; 45,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,63; -29,66</t>
+          <t>-68,18; -25,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,7; 176,22</t>
+          <t>61,43; 162,32</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,56</t>
+          <t>10,01</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,08</t>
+          <t>8,04</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9,27</t>
+          <t>8,98</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 9,01</t>
+          <t>2,11; 9,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,38</t>
+          <t>-2,79; 1,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,12; 14,54</t>
+          <t>6,89; 13,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 8,92</t>
+          <t>1,88; 8,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 3,31</t>
+          <t>-1,91; 3,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,7; 11,31</t>
+          <t>5,1; 11,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,93</t>
+          <t>2,78; 7,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 1,72</t>
+          <t>-1,96; 1,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,94; 11,87</t>
+          <t>6,48; 11,37</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>486,48%</t>
+          <t>461,2%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>283,62%</t>
+          <t>282,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>367,94%</t>
+          <t>356,4%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42,22; 713,24</t>
+          <t>37,33; 844,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-77,94; 201,33</t>
+          <t>-80,5; 182,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>184,77; 1456,1</t>
+          <t>169,51; 1420,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34,59; 530,91</t>
+          <t>37,78; 510,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-51,27; 223,08</t>
+          <t>-49,63; 239,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>95,81; 736,46</t>
+          <t>106,82; 719,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>74,73; 440,75</t>
+          <t>69,81; 445,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,71; 102,44</t>
+          <t>-54,51; 91,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>176,53; 692,19</t>
+          <t>172,16; 703,5</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,49</t>
+          <t>4,53</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,2</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>2,04</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 6,62</t>
+          <t>1,03; 6,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,87; 9,53</t>
+          <t>3,21; 9,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 8,91</t>
+          <t>1,32; 8,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 8,22</t>
+          <t>0,7; 8,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,07; 10,36</t>
+          <t>2,08; 10,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 1,91</t>
+          <t>-3,24; 2,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 6,44</t>
+          <t>1,63; 6,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,33; 9,1</t>
+          <t>3,44; 8,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,95</t>
+          <t>-0,17; 4,64</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>195,41%</t>
+          <t>196,95%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-23,83%</t>
+          <t>-5,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>55,23%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,67; 524,02</t>
+          <t>20,59; 546,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>78,51; 723,9</t>
+          <t>85,15; 794,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30,22; 696,02</t>
+          <t>41,48; 623,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,06; 233,71</t>
+          <t>8,38; 238,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,15; 288,56</t>
+          <t>28,96; 289,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-61,37; 56,83</t>
+          <t>-49,38; 85,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,94; 230,74</t>
+          <t>32,91; 239,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>64,12; 316,36</t>
+          <t>70,28; 320,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 143,36</t>
+          <t>-8,08; 161,53</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>-1,29</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,87</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,91</t>
+          <t>-1,27</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 11,34</t>
+          <t>-0,85; 11,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 4,22</t>
+          <t>-5,9; 4,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 3,78</t>
+          <t>-5,83; 3,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,29; 16,52</t>
+          <t>2,82; 16,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 2,28</t>
+          <t>-8,47; 2,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 1,91</t>
+          <t>-7,03; 3,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,12; 12,34</t>
+          <t>2,57; 12,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 1,8</t>
+          <t>-5,71; 1,49</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 1,22</t>
+          <t>-4,77; 2,11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-11,25%</t>
+          <t>-15,76%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-28,75%</t>
+          <t>-13,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-21,09%</t>
+          <t>-13,97%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 191,96</t>
+          <t>-10,73; 207,88</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-55,67; 85,64</t>
+          <t>-56,44; 89,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-52,84; 71,38</t>
+          <t>-54,01; 60,14</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,95; 243,16</t>
+          <t>19,42; 253,44</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-64,67; 35,14</t>
+          <t>-65,16; 40,39</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-64,88; 27,48</t>
+          <t>-49,96; 50,47</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,9; 168,0</t>
+          <t>20,99; 165,47</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-53,46; 30,87</t>
+          <t>-51,29; 23,34</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-51,83; 16,62</t>
+          <t>-40,27; 31,17</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20,44</t>
+          <t>20,16</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,05</t>
+          <t>16,78</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18,75</t>
+          <t>18,47</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,57; 8,67</t>
+          <t>2,5; 8,87</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,29; 11,52</t>
+          <t>4,46; 11,61</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16,15; 25,06</t>
+          <t>15,94; 24,23</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,32; 12,95</t>
+          <t>4,8; 13,4</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,61; 11,21</t>
+          <t>2,47; 10,77</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,8; 21,46</t>
+          <t>12,67; 20,99</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,57; 9,82</t>
+          <t>4,44; 9,95</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>4,59; 10,29</t>
+          <t>4,55; 9,94</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>15,74; 21,88</t>
+          <t>15,6; 21,8</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2865,47%</t>
+          <t>2827,01%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>655,78%</t>
+          <t>645,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1123,27%</t>
+          <t>1106,47%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>44,85; —</t>
+          <t>44,96; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>208,36; —</t>
+          <t>164,03; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>747,81; —</t>
+          <t>661,72; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>93,9; 929,76</t>
+          <t>89,0; 941,19</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>48,15; 814,88</t>
+          <t>43,3; 680,26</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>276,61; 1581,83</t>
+          <t>277,27; 1644,59</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>155,84; 1020,67</t>
+          <t>154,42; 1126,58</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>171,37; 1076,21</t>
+          <t>152,35; 1122,64</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>557,99; 2586,94</t>
+          <t>536,52; 2410,62</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>5,71</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,26</t>
+          <t>8,53</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>18,6</t>
+          <t>7,17</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 3,69</t>
+          <t>-1,85; 3,8</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,92</t>
+          <t>-3,64; 1,15</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,58; 8,45</t>
+          <t>2,71; 9,03</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 5,11</t>
+          <t>-1,03; 4,85</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 3,1</t>
+          <t>-2,54; 2,83</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,53; 61,91</t>
+          <t>5,45; 11,45</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,69</t>
+          <t>-0,33; 3,46</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,38</t>
+          <t>-2,53; 1,13</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,58; 44,69</t>
+          <t>5,18; 9,32</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>101,44%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>494,8%</t>
+          <t>149,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>327,94%</t>
+          <t>126,43%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-23,96; 85,27</t>
+          <t>-28,66; 83,85</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-56,11; 25,35</t>
+          <t>-53,03; 31,85</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>34,92; 184,37</t>
+          <t>38,26; 198,22</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 111,91</t>
+          <t>-16,11; 113,87</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-31,4; 72,72</t>
+          <t>-36,59; 63,98</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>103,12; 1319,78</t>
+          <t>70,03; 260,79</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 76,34</t>
+          <t>-5,81; 71,34</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-35,67; 30,32</t>
+          <t>-38,36; 22,84</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>92,58; 895,78</t>
+          <t>75,48; 207,35</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-1,94</t>
+          <t>-0,47</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,97</t>
+          <t>-0,65</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-1,73</t>
+          <t>-0,57</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,69</t>
+          <t>-2,39; 3,07</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 2,89</t>
+          <t>-2,14; 3,09</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 0,95</t>
+          <t>-2,79; 2,29</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,97; -0,48</t>
+          <t>-6,03; -0,12</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 1,01</t>
+          <t>-4,68; 1,1</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 1,45</t>
+          <t>-3,51; 1,96</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 0,39</t>
+          <t>-3,43; 0,32</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,37</t>
+          <t>-2,66; 1,1</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 0,32</t>
+          <t>-2,49; 1,27</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-29,45%</t>
+          <t>-7,12%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-10,3%</t>
+          <t>-6,97%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-21,58%</t>
+          <t>-7,12%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-32,6; 52,09</t>
+          <t>-30,81; 60,33</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-30,71; 54,2</t>
+          <t>-28,28; 59,22</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-73,7; 14,87</t>
+          <t>-36,84; 46,04</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-55,46; -4,98</t>
+          <t>-54,43; -0,07</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-45,66; 13,37</t>
+          <t>-42,89; 14,61</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-35,25; 18,5</t>
+          <t>-32,43; 24,59</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-38,47; 5,99</t>
+          <t>-39,21; 4,32</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-30,92; 18,19</t>
+          <t>-29,52; 15,72</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-51,35; 3,12</t>
+          <t>-27,71; 18,29</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,87</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,47</t>
+          <t>5,18</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>7,56</t>
+          <t>5,52</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,39</t>
+          <t>1,17; 3,55</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,62</t>
+          <t>-0,53; 1,65</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,95</t>
+          <t>4,52; 7,28</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,19</t>
+          <t>1,4; 4,05</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,92</t>
+          <t>-0,68; 1,68</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,22; 24,02</t>
+          <t>3,92; 6,36</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,56</t>
+          <t>1,69; 3,51</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,46</t>
+          <t>-0,17; 1,42</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>4,66; 15,84</t>
+          <t>4,63; 6,42</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>109,53%</t>
+          <t>117,5%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>151,36%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>134,04%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>17,2; 76,62</t>
+          <t>20,1; 77,28</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 36,56</t>
+          <t>-9,85; 36,58</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>62,04; 154,33</t>
+          <t>80,42; 164,08</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>20,45; 73,41</t>
+          <t>20,11; 71,73</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 33,54</t>
+          <t>-10,08; 29,19</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>66,08; 418,22</t>
+          <t>56,55; 112,98</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>28,35; 67,2</t>
+          <t>27,45; 65,99</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 27,8</t>
+          <t>-2,75; 27,4</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>80,62; 298,72</t>
+          <t>77,09; 121,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_fisi_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
